--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D105"/>
+  <dimension ref="A1:D109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2051,20 +2051,14 @@
           <t>WlhYT07d</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="B102" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C102" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D102" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="103">
@@ -2073,20 +2067,14 @@
           <t>SzxylMbS</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="B103" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C103" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D103" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="104">
@@ -2095,20 +2083,14 @@
           <t>bHLf4sq9</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="B104" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C104" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D104" t="n">
+        <v>2.15</v>
       </c>
     </row>
     <row r="105">
@@ -2117,19 +2099,101 @@
           <t>f9bfyqFM</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C105" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D105" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>AZ3PVMxp</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
         <is>
           <t>1.55</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>5.75</t>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>hvcjgHz8</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>dnnqk0iD</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>QT6wuRFc</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>5.00</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D109"/>
+  <dimension ref="A1:D139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2115,20 +2115,14 @@
           <t>AZ3PVMxp</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
+      <c r="B106" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C106" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D106" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="107">
@@ -2137,20 +2131,14 @@
           <t>hvcjgHz8</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
+      <c r="B107" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C107" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D107" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="108">
@@ -2159,20 +2147,14 @@
           <t>dnnqk0iD</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
+      <c r="B108" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="C108" t="n">
+        <v>5</v>
+      </c>
+      <c r="D108" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="109">
@@ -2181,19 +2163,673 @@
           <t>QT6wuRFc</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B109" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C109" t="n">
+        <v>4</v>
+      </c>
+      <c r="D109" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>YH892O2B</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>8jyraADG</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>4xHh663n</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>6RvR2hEi</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>0lGMiS5j</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>hKOA02XN</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>O2Fteteo</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>Sf88FVcc</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>8KIdPmPc</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>fNwTkrUF</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>42SH31wI</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>Aeu0r0Mk</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>ALOjHNNj</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>ILr8tvi2</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>bepKi4a3</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>6sP22LDL</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>dC3sew6e</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>Ob5Zdayq</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>02s0k9od</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>bs5ow5pA</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>tYhtcc5C</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>x0nkeyzP</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
         <is>
           <t>1.65</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>SORbFvLt</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
         <is>
           <t>4.00</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>5.00</t>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>lvG7DIkg</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>IXMN9zkI</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>EL1P0u6m</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>M5TEBdK5</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t>joLV7EJU</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>WvwvCQVo</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>8KfYbJz0</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2.40</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D109"/>
+  <dimension ref="A1:D141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2115,20 +2115,14 @@
           <t>AZ3PVMxp</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
+      <c r="B106" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C106" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D106" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="107">
@@ -2137,20 +2131,14 @@
           <t>hvcjgHz8</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
+      <c r="B107" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C107" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D107" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="108">
@@ -2159,20 +2147,14 @@
           <t>dnnqk0iD</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
+      <c r="B108" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="C108" t="n">
+        <v>5</v>
+      </c>
+      <c r="D108" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="109">
@@ -2181,19 +2163,537 @@
           <t>QT6wuRFc</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
+      <c r="B109" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C109" t="n">
+        <v>4</v>
+      </c>
+      <c r="D109" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>YH892O2B</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C110" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D110" t="n">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>8jyraADG</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C111" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D111" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>4xHh663n</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C112" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D112" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>6RvR2hEi</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C113" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D113" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>0lGMiS5j</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C114" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D114" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>hKOA02XN</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C115" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D115" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>O2Fteteo</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>7</v>
+      </c>
+      <c r="C116" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D116" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>Sf88FVcc</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C117" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D117" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>8KIdPmPc</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C118" t="n">
+        <v>5</v>
+      </c>
+      <c r="D118" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>fNwTkrUF</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C119" t="n">
+        <v>3</v>
+      </c>
+      <c r="D119" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>42SH31wI</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C120" t="n">
+        <v>4</v>
+      </c>
+      <c r="D120" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>Aeu0r0Mk</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C121" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D121" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>ALOjHNNj</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C122" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D122" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>ILr8tvi2</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C123" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D123" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>bepKi4a3</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C124" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D124" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>6sP22LDL</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>3</v>
+      </c>
+      <c r="C125" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D125" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>dC3sew6e</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="C126" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D126" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>Ob5Zdayq</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C127" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D127" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>02s0k9od</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C128" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D128" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>bs5ow5pA</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C129" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D129" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>tYhtcc5C</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C130" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D130" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>x0nkeyzP</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C131" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D131" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>SORbFvLt</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>4</v>
+      </c>
+      <c r="C132" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D132" t="n">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>lvG7DIkg</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>3</v>
+      </c>
+      <c r="C133" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D133" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>IXMN9zkI</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C134" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D134" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>EL1P0u6m</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C135" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D135" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>M5TEBdK5</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C136" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D136" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t>joLV7EJU</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C137" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D137" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>WvwvCQVo</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C138" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D138" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>8KfYbJz0</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>3</v>
+      </c>
+      <c r="C139" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D139" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>EirZ0Wr4</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
         <is>
           <t>4.00</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>5.00</t>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="inlineStr">
+        <is>
+          <t>t4ZkclrT</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2.10</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D141"/>
+  <dimension ref="A1:D145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2659,20 +2659,14 @@
           <t>EirZ0Wr4</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="B140" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C140" t="n">
+        <v>4</v>
+      </c>
+      <c r="D140" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="141">
@@ -2681,19 +2675,101 @@
           <t>t4ZkclrT</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
+      <c r="B141" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C141" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D141" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="inlineStr">
+        <is>
+          <t>8x0Cb1B6</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="inlineStr">
+        <is>
+          <t>GrNwFMem</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>CjGqFjre</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
         <is>
           <t>3.40</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>2.10</t>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>4CX22Dbk</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>3.60</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D145"/>
+  <dimension ref="A1:D155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2691,20 +2691,14 @@
           <t>8x0Cb1B6</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
+      <c r="B142" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C142" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.6</v>
       </c>
     </row>
     <row r="143">
@@ -2713,20 +2707,14 @@
           <t>GrNwFMem</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="B143" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C143" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D143" t="n">
+        <v>2.35</v>
       </c>
     </row>
     <row r="144">
@@ -2735,20 +2723,14 @@
           <t>CjGqFjre</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B144" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C144" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D144" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="145">
@@ -2757,19 +2739,233 @@
           <t>4CX22Dbk</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
+      <c r="B145" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C145" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D145" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>M7MVoOR0</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>dbt7KrYP</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
         <is>
           <t>3.10</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>AsIP75lK</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>6D3e2qCs</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>0IkylEqd</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>CEhO9e6F</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
         <is>
           <t>3.60</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>CxyB0iT1</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>CSXdOfL8</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>ptW4MYkL</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>4QCyHCDr</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>3.40</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D155"/>
+  <dimension ref="A1:D161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2755,20 +2755,14 @@
           <t>M7MVoOR0</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
+      <c r="B146" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C146" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D146" t="n">
+        <v>6.25</v>
       </c>
     </row>
     <row r="147">
@@ -2777,20 +2771,14 @@
           <t>dbt7KrYP</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="B147" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C147" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D147" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="148">
@@ -2799,20 +2787,14 @@
           <t>AsIP75lK</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>12.00</t>
-        </is>
+      <c r="B148" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C148" t="n">
+        <v>7</v>
+      </c>
+      <c r="D148" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="149">
@@ -2821,20 +2803,14 @@
           <t>6D3e2qCs</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
+      <c r="B149" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C149" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D149" t="n">
+        <v>2.88</v>
       </c>
     </row>
     <row r="150">
@@ -2843,20 +2819,14 @@
           <t>0IkylEqd</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="B150" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C150" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D150" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="151">
@@ -2865,20 +2835,14 @@
           <t>CEhO9e6F</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
+      <c r="B151" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C151" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D151" t="n">
+        <v>5.75</v>
       </c>
     </row>
     <row r="152">
@@ -2887,20 +2851,14 @@
           <t>CxyB0iT1</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="B152" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C152" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D152" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="153">
@@ -2909,20 +2867,14 @@
           <t>CSXdOfL8</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B153" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C153" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D153" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="154">
@@ -2931,20 +2883,14 @@
           <t>ptW4MYkL</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="B154" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C154" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D154" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="155">
@@ -2953,19 +2899,145 @@
           <t>4QCyHCDr</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B155" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C155" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D155" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
+          <t>fZZxp2dD</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>0hYMmpcl</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>UilLdutJ</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t>2uc40Ntf</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>hCxNBHy3</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
         <is>
           <t>2.15</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="inlineStr">
+        <is>
+          <t>KvdW7ZzS</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
         <is>
           <t>3.30</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>3.40</t>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>3.10</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D161"/>
+  <dimension ref="A1:D173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2915,20 +2915,14 @@
           <t>fZZxp2dD</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
+      <c r="B156" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C156" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1.85</v>
       </c>
     </row>
     <row r="157">
@@ -2937,20 +2931,14 @@
           <t>0hYMmpcl</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="B157" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C157" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D157" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="158">
@@ -2959,20 +2947,14 @@
           <t>UilLdutJ</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
+      <c r="B158" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C158" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D158" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="159">
@@ -2981,20 +2963,14 @@
           <t>2uc40Ntf</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="B159" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C159" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D159" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="160">
@@ -3003,20 +2979,14 @@
           <t>hCxNBHy3</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="B160" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C160" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D160" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="161">
@@ -3025,19 +2995,277 @@
           <t>KvdW7ZzS</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
+      <c r="B161" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C161" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D161" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="inlineStr">
+        <is>
+          <t>WdSjHeFt</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>EaryFQkA</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
         <is>
           <t>3.30</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>zVpmZBZQ</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>SSPRRTR0</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>p4dhrkCs</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>Y54hDUC7</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>v3ivyY4E</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>W0WITkcl</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
         <is>
           <t>3.10</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>YPSZP7dD</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t>EL5MmBlK</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>tWk1tTtf</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>Eql9v7B6</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2.90</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D173"/>
+  <dimension ref="A1:D181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3011,20 +3011,14 @@
           <t>WdSjHeFt</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
+      <c r="B162" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C162" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D162" t="n">
+        <v>6.25</v>
       </c>
     </row>
     <row r="163">
@@ -3033,20 +3027,14 @@
           <t>EaryFQkA</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="B163" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C163" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D163" t="n">
+        <v>2.2</v>
       </c>
     </row>
     <row r="164">
@@ -3055,20 +3043,14 @@
           <t>zVpmZBZQ</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B164" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C164" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D164" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="165">
@@ -3077,20 +3059,14 @@
           <t>SSPRRTR0</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="B165" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C165" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D165" t="n">
+        <v>2.8</v>
       </c>
     </row>
     <row r="166">
@@ -3099,20 +3075,14 @@
           <t>p4dhrkCs</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B166" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C166" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D166" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="167">
@@ -3121,20 +3091,14 @@
           <t>Y54hDUC7</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="B167" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C167" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D167" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="168">
@@ -3143,20 +3107,14 @@
           <t>v3ivyY4E</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="B168" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C168" t="n">
+        <v>3</v>
+      </c>
+      <c r="D168" t="n">
+        <v>2.4</v>
       </c>
     </row>
     <row r="169">
@@ -3165,20 +3123,14 @@
           <t>W0WITkcl</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="B169" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C169" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D169" t="n">
+        <v>2.1</v>
       </c>
     </row>
     <row r="170">
@@ -3187,20 +3139,14 @@
           <t>YPSZP7dD</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
+      <c r="B170" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C170" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D170" t="n">
+        <v>3.8</v>
       </c>
     </row>
     <row r="171">
@@ -3209,20 +3155,14 @@
           <t>EL5MmBlK</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="B171" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C171" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D171" t="n">
+        <v>2.9</v>
       </c>
     </row>
     <row r="172">
@@ -3231,20 +3171,14 @@
           <t>tWk1tTtf</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="B172" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C172" t="n">
+        <v>3</v>
+      </c>
+      <c r="D172" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="173">
@@ -3253,19 +3187,189 @@
           <t>Eql9v7B6</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
+      <c r="B173" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C173" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D173" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>0xK7DDE5</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>ELeQ0zVa</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>d4DGBiqI</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>dtLQNtsB</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
         <is>
           <t>3.25</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr">
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>Ofy73Ced</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>CGH1PgIF</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>21OYHBAk</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
         <is>
           <t>2.90</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="inlineStr">
+        <is>
+          <t>v3JgRFm3</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>3.70</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D181"/>
+  <dimension ref="A1:D191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3203,20 +3203,14 @@
           <t>0xK7DDE5</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="B174" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C174" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D174" t="n">
+        <v>2.55</v>
       </c>
     </row>
     <row r="175">
@@ -3225,20 +3219,14 @@
           <t>ELeQ0zVa</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B175" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C175" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D175" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="176">
@@ -3247,20 +3235,14 @@
           <t>d4DGBiqI</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="B176" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C176" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D176" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="177">
@@ -3269,20 +3251,14 @@
           <t>dtLQNtsB</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="B177" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C177" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D177" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="178">
@@ -3291,20 +3267,14 @@
           <t>Ofy73Ced</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B178" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C178" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D178" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="179">
@@ -3313,20 +3283,14 @@
           <t>CGH1PgIF</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="B179" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C179" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D179" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="180">
@@ -3335,20 +3299,14 @@
           <t>21OYHBAk</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
+      <c r="B180" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C180" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D180" t="n">
+        <v>3.75</v>
       </c>
     </row>
     <row r="181">
@@ -3357,19 +3315,233 @@
           <t>v3JgRFm3</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="B181" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C181" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D181" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>hCGaFZqg</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>6ZvTGnLc</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>nZgYbEaC</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t>r1mschUO</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t>SjzlgqTj</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>v5l07LdU</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
         <is>
           <t>2.10</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>fHO9ROsn</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
         <is>
           <t>3.20</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>3.70</t>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t>jqIIP2Cb</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>GUXb5YQq</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t>WIX2NXnS</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>3.00</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D199"/>
+  <dimension ref="A1:D211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3491,20 +3491,14 @@
           <t>v1I9TP43</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
+      <c r="B192" t="n">
+        <v>6</v>
+      </c>
+      <c r="C192" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D192" t="n">
+        <v>1.6</v>
       </c>
     </row>
     <row r="193">
@@ -3513,20 +3507,14 @@
           <t>n7VN5MCd</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="B193" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C193" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D193" t="n">
+        <v>2.55</v>
       </c>
     </row>
     <row r="194">
@@ -3535,20 +3523,14 @@
           <t>OGCsGku2</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="B194" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C194" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D194" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="195">
@@ -3557,20 +3539,14 @@
           <t>jN4TwgX8</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="B195" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C195" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D195" t="n">
+        <v>2.9</v>
       </c>
     </row>
     <row r="196">
@@ -3579,20 +3555,14 @@
           <t>OUiGUlfe</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
+      <c r="B196" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C196" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D196" t="n">
+        <v>2.88</v>
       </c>
     </row>
     <row r="197">
@@ -3601,20 +3571,14 @@
           <t>CjYAjWGE</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="B197" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C197" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D197" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="198">
@@ -3623,20 +3587,14 @@
           <t>b7WIlAoR</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="B198" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C198" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D198" t="n">
+        <v>2.55</v>
       </c>
     </row>
     <row r="199">
@@ -3645,19 +3603,277 @@
           <t>S2b7WAPr</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
+      <c r="B199" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C199" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D199" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="inlineStr">
+        <is>
+          <t>rgFQPs4S</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>WIJkQBF8</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>Esk5Iad2</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>6cNF7rrp</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>zFWqD4KM</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>4WHcOkpL</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>zTBIR3ZF</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>SQjcKLRk</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>j5BcsSw1</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>WWCyxX1L</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>WfeOSSO7</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>IiDkql9l</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
         <is>
           <t>2.90</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>3.40</t>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>3.20</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D199"/>
+  <dimension ref="A1:D230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3491,20 +3491,14 @@
           <t>v1I9TP43</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
+      <c r="B192" t="n">
+        <v>6</v>
+      </c>
+      <c r="C192" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D192" t="n">
+        <v>1.6</v>
       </c>
     </row>
     <row r="193">
@@ -3513,20 +3507,14 @@
           <t>n7VN5MCd</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="B193" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C193" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D193" t="n">
+        <v>2.55</v>
       </c>
     </row>
     <row r="194">
@@ -3535,20 +3523,14 @@
           <t>OGCsGku2</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="B194" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C194" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D194" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="195">
@@ -3557,20 +3539,14 @@
           <t>jN4TwgX8</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="B195" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C195" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D195" t="n">
+        <v>2.9</v>
       </c>
     </row>
     <row r="196">
@@ -3579,20 +3555,14 @@
           <t>OUiGUlfe</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
+      <c r="B196" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C196" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D196" t="n">
+        <v>2.88</v>
       </c>
     </row>
     <row r="197">
@@ -3601,20 +3571,14 @@
           <t>CjYAjWGE</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="B197" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C197" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D197" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="198">
@@ -3623,20 +3587,14 @@
           <t>b7WIlAoR</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="B198" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C198" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D198" t="n">
+        <v>2.55</v>
       </c>
     </row>
     <row r="199">
@@ -3645,19 +3603,611 @@
           <t>S2b7WAPr</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
+      <c r="B199" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C199" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D199" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="inlineStr">
+        <is>
+          <t>drYOcmOs</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C200" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D200" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>48yXeRhf</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C201" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D201" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>YL6GgdTN</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C202" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D202" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>0zVuf5N6</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C203" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D203" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>CAdh390K</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C204" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D204" t="n">
+        <v>2.63</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>YmTmhqhJ</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C205" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D205" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>dGBia0an</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C206" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D206" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>4tFacvUb</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C207" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D207" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>Qe38eIbB</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C208" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D208" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>nX46u68D</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C209" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D209" t="n">
+        <v>2.63</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>j5BcsSw1</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C210" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D210" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>WWCyxX1L</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C211" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D211" t="n">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>WfeOSSO7</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C212" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D212" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="inlineStr">
+        <is>
+          <t>IiDkql9l</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C213" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D213" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>xIieTySH</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>WvDUsysB</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>pOEMqcCb</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>A50vXJSh</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>O8QDoJsn</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
         <is>
           <t>3.40</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t>Yqo4RFdU</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t>S66wtFBN</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>44gmVcc5</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>2ucWYubt</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>rgFQPs4S</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>WIJkQBF8</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>Esk5Iad2</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>6cNF7rrp</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>zFWqD4KM</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>4WHcOkpL</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>zTBIR3ZF</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>SQjcKLRk</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>11.00</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D230"/>
+  <dimension ref="A1:D239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3843,20 +3843,14 @@
           <t>xIieTySH</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B214" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C214" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D214" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="215">
@@ -3865,20 +3859,14 @@
           <t>WvDUsysB</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="B215" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C215" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D215" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="216">
@@ -3887,20 +3875,14 @@
           <t>pOEMqcCb</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
+      <c r="B216" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C216" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="D216" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="217">
@@ -3909,20 +3891,14 @@
           <t>A50vXJSh</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B217" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C217" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D217" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="218">
@@ -3931,20 +3907,14 @@
           <t>O8QDoJsn</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="B218" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C218" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D218" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="219">
@@ -3953,20 +3923,14 @@
           <t>Yqo4RFdU</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="B219" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C219" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D219" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="220">
@@ -3975,20 +3939,14 @@
           <t>S66wtFBN</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
+      <c r="B220" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C220" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D220" t="n">
+        <v>2.63</v>
       </c>
     </row>
     <row r="221">
@@ -3997,20 +3955,14 @@
           <t>44gmVcc5</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="B221" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C221" t="n">
+        <v>3</v>
+      </c>
+      <c r="D221" t="n">
+        <v>2.75</v>
       </c>
     </row>
     <row r="222">
@@ -4019,20 +3971,14 @@
           <t>2ucWYubt</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="B222" t="n">
+        <v>2</v>
+      </c>
+      <c r="C222" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D222" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="223">
@@ -4041,20 +3987,14 @@
           <t>rgFQPs4S</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
+      <c r="B223" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C223" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D223" t="n">
+        <v>6.25</v>
       </c>
     </row>
     <row r="224">
@@ -4063,20 +4003,14 @@
           <t>WIJkQBF8</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
+      <c r="B224" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C224" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D224" t="n">
+        <v>3.25</v>
       </c>
     </row>
     <row r="225">
@@ -4085,20 +4019,14 @@
           <t>Esk5Iad2</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
+      <c r="B225" t="n">
+        <v>8</v>
+      </c>
+      <c r="C225" t="n">
+        <v>5</v>
+      </c>
+      <c r="D225" t="n">
+        <v>1.38</v>
       </c>
     </row>
     <row r="226">
@@ -4107,20 +4035,14 @@
           <t>6cNF7rrp</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
+      <c r="B226" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C226" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D226" t="n">
+        <v>1.75</v>
       </c>
     </row>
     <row r="227">
@@ -4129,20 +4051,14 @@
           <t>zFWqD4KM</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="B227" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C227" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D227" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="228">
@@ -4151,20 +4067,14 @@
           <t>4WHcOkpL</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
+      <c r="B228" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C228" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D228" t="n">
+        <v>4.1</v>
       </c>
     </row>
     <row r="229">
@@ -4173,20 +4083,14 @@
           <t>zTBIR3ZF</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="B229" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C229" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D229" t="n">
+        <v>2.2</v>
       </c>
     </row>
     <row r="230">
@@ -4195,19 +4099,211 @@
           <t>SQjcKLRk</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
+      <c r="B230" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C230" t="n">
+        <v>6</v>
+      </c>
+      <c r="D230" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>OAeKROjD</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>h8xCR9dC</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
         <is>
           <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>OE5MGhrf</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>baMp22np</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>xCj1xWPj</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>h2uVDr1f</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>SG7bDmCr</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>WjBv9U0S</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>O2Xm0vko</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>4.75</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D239"/>
+  <dimension ref="A1:D247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4115,20 +4115,14 @@
           <t>OAeKROjD</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
+      <c r="B231" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C231" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D231" t="n">
+        <v>5.75</v>
       </c>
     </row>
     <row r="232">
@@ -4137,20 +4131,14 @@
           <t>h8xCR9dC</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
+      <c r="B232" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C232" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D232" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="233">
@@ -4159,20 +4147,14 @@
           <t>OE5MGhrf</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="B233" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C233" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D233" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="234">
@@ -4181,20 +4163,14 @@
           <t>baMp22np</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B234" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C234" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D234" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="235">
@@ -4203,20 +4179,14 @@
           <t>xCj1xWPj</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
+      <c r="B235" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C235" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D235" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="236">
@@ -4225,20 +4195,14 @@
           <t>h2uVDr1f</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="B236" t="n">
+        <v>2</v>
+      </c>
+      <c r="C236" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D236" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="237">
@@ -4247,20 +4211,14 @@
           <t>SG7bDmCr</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
+      <c r="B237" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C237" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D237" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="238">
@@ -4269,20 +4227,14 @@
           <t>WjBv9U0S</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B238" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C238" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D238" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="239">
@@ -4291,19 +4243,189 @@
           <t>O2Xm0vko</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>4.75</t>
+      <c r="B239" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C239" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D239" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>Whh3dzd4</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>KIQjmWIj</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>pIgDNCf3</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>CCDxBZAc</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>jwmmlzio</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>vaTsAHD4</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>4USV4sgM</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>8vLb6ZCT</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>2.90</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D247"/>
+  <dimension ref="A1:D256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4259,20 +4259,14 @@
           <t>Whh3dzd4</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
+      <c r="B240" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C240" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D240" t="n">
+        <v>2.63</v>
       </c>
     </row>
     <row r="241">
@@ -4281,20 +4275,14 @@
           <t>KIQjmWIj</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
+      <c r="B241" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C241" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D241" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="242">
@@ -4303,20 +4291,14 @@
           <t>pIgDNCf3</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
+      <c r="B242" t="n">
+        <v>7</v>
+      </c>
+      <c r="C242" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D242" t="n">
+        <v>1.45</v>
       </c>
     </row>
     <row r="243">
@@ -4325,20 +4307,14 @@
           <t>CCDxBZAc</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>9.50</t>
-        </is>
+      <c r="B243" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="C243" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D243" t="n">
+        <v>9.5</v>
       </c>
     </row>
     <row r="244">
@@ -4347,20 +4323,14 @@
           <t>jwmmlzio</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="B244" t="n">
+        <v>2</v>
+      </c>
+      <c r="C244" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D244" t="n">
+        <v>3.9</v>
       </c>
     </row>
     <row r="245">
@@ -4369,20 +4339,14 @@
           <t>vaTsAHD4</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="B245" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C245" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D245" t="n">
+        <v>2.55</v>
       </c>
     </row>
     <row r="246">
@@ -4391,20 +4355,14 @@
           <t>4USV4sgM</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="B246" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C246" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D246" t="n">
+        <v>3.7</v>
       </c>
     </row>
     <row r="247">
@@ -4413,19 +4371,211 @@
           <t>8vLb6ZCT</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
+      <c r="B247" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C247" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D247" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>WETw9DuA</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>0YqKhheT</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
         <is>
           <t>3.30</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr">
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>OC8I1VXq</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>h8tCfEQG</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>WxCQa92d</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>nPWk8erH</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>ID6U0Dzi</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
         <is>
           <t>2.90</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>zkyF8Pgc</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>82ZM63O9</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>3.80</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D268"/>
+  <dimension ref="A1:D279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4579,20 +4579,14 @@
           <t>EB8yv2aJ</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
+      <c r="B260" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C260" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D260" t="n">
+        <v>7.5</v>
       </c>
     </row>
     <row r="261">
@@ -4601,20 +4595,14 @@
           <t>WUqjkmPH</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B261" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C261" t="n">
+        <v>3</v>
+      </c>
+      <c r="D261" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="262">
@@ -4623,20 +4611,14 @@
           <t>8SWavWAa</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
+      <c r="B262" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C262" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D262" t="n">
+        <v>2.88</v>
       </c>
     </row>
     <row r="263">
@@ -4645,20 +4627,14 @@
           <t>z3jsi9f5</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="B263" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C263" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D263" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="264">
@@ -4667,20 +4643,14 @@
           <t>xd6CHKxS</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="B264" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C264" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D264" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="265">
@@ -4689,20 +4659,14 @@
           <t>8xjWXuN8</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="B265" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C265" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D265" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="266">
@@ -4711,20 +4675,14 @@
           <t>8zBCDByf</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B266" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C266" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D266" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="267">
@@ -4733,20 +4691,14 @@
           <t>tl9KBk66</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="B267" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C267" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D267" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="268">
@@ -4755,19 +4707,255 @@
           <t>EyI3FX6s</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
+      <c r="B268" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C268" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D268" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>SIOithtm</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
         <is>
           <t>3.30</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr">
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>lnhZhVPh</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>dzYLoEIP</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>SW3Qfiet</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>x8OGzlAO</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>ttV7xAuC</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
         <is>
           <t>5.00</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>tAM9caod</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>8GEeL2w3</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>4r84Jt8F</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>KG9yCb0k</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>StDqAxV1</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>3.80</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D279"/>
+  <dimension ref="A1:D288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4723,20 +4723,14 @@
           <t>SIOithtm</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
+      <c r="B269" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C269" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D269" t="n">
+        <v>2.05</v>
       </c>
     </row>
     <row r="270">
@@ -4745,20 +4739,14 @@
           <t>lnhZhVPh</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
+      <c r="B270" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C270" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D270" t="n">
+        <v>1.95</v>
       </c>
     </row>
     <row r="271">
@@ -4767,20 +4755,14 @@
           <t>dzYLoEIP</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="B271" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C271" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D271" t="n">
+        <v>3.7</v>
       </c>
     </row>
     <row r="272">
@@ -4789,20 +4771,14 @@
           <t>SW3Qfiet</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
+      <c r="B272" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C272" t="n">
+        <v>4</v>
+      </c>
+      <c r="D272" t="n">
+        <v>6.25</v>
       </c>
     </row>
     <row r="273">
@@ -4811,20 +4787,14 @@
           <t>x8OGzlAO</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
+      <c r="B273" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C273" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D273" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="274">
@@ -4833,20 +4803,14 @@
           <t>ttV7xAuC</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
+      <c r="B274" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C274" t="n">
+        <v>5</v>
+      </c>
+      <c r="D274" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="275">
@@ -4855,20 +4819,14 @@
           <t>tAM9caod</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="B275" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C275" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D275" t="n">
+        <v>2.8</v>
       </c>
     </row>
     <row r="276">
@@ -4877,20 +4835,14 @@
           <t>8GEeL2w3</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="B276" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C276" t="n">
+        <v>3</v>
+      </c>
+      <c r="D276" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="277">
@@ -4899,20 +4851,14 @@
           <t>4r84Jt8F</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
+      <c r="B277" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C277" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D277" t="n">
+        <v>3.75</v>
       </c>
     </row>
     <row r="278">
@@ -4921,20 +4867,14 @@
           <t>KG9yCb0k</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="B278" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C278" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D278" t="n">
+        <v>2.55</v>
       </c>
     </row>
     <row r="279">
@@ -4943,19 +4883,211 @@
           <t>StDqAxV1</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr">
+      <c r="B279" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C279" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D279" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>SznSCTAl</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>Cl5M5C3L</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>EXLhbUee</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
         <is>
           <t>1.95</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr">
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>4MfFXWSP</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
         <is>
           <t>3.40</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>3.80</t>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>Imw2OSkC</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>UR6KtA5t</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>dvbywS45</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>441qy6ZH</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>xG2T9TzJ</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>4.50</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D288"/>
+  <dimension ref="A1:D299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4899,20 +4899,14 @@
           <t>SznSCTAl</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>9.00</t>
-        </is>
+      <c r="B280" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C280" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D280" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="281">
@@ -4921,20 +4915,14 @@
           <t>Cl5M5C3L</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="B281" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C281" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D281" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="282">
@@ -4943,20 +4931,14 @@
           <t>EXLhbUee</t>
         </is>
       </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
+      <c r="B282" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C282" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D282" t="n">
+        <v>1.95</v>
       </c>
     </row>
     <row r="283">
@@ -4965,20 +4947,14 @@
           <t>4MfFXWSP</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
+      <c r="B283" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C283" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D283" t="n">
+        <v>2.05</v>
       </c>
     </row>
     <row r="284">
@@ -4987,20 +4963,14 @@
           <t>Imw2OSkC</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="B284" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C284" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D284" t="n">
+        <v>2.8</v>
       </c>
     </row>
     <row r="285">
@@ -5009,20 +4979,14 @@
           <t>UR6KtA5t</t>
         </is>
       </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B285" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C285" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D285" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="286">
@@ -5031,20 +4995,14 @@
           <t>dvbywS45</t>
         </is>
       </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="B286" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C286" t="n">
+        <v>3</v>
+      </c>
+      <c r="D286" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="287">
@@ -5053,20 +5011,14 @@
           <t>441qy6ZH</t>
         </is>
       </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
+      <c r="B287" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C287" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="D287" t="n">
+        <v>3.25</v>
       </c>
     </row>
     <row r="288">
@@ -5075,19 +5027,195 @@
           <t>xG2T9TzJ</t>
         </is>
       </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>4.50</t>
+      <c r="B288" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C288" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D288" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>0lpzB7u1</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>4</v>
+      </c>
+      <c r="C289" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D289" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>GMBD7YY8</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C290" t="n">
+        <v>3</v>
+      </c>
+      <c r="D290" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>AJ5eIkmR</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C291" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D291" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>dGwq9oAD</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="C292" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D292" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>8Kjh0jRr</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="C293" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D293" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>2g2mKBIE</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C294" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D294" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>MLqgQlLa</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C295" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D295" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>lfWoSAjm</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C296" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D296" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>j1yAM6KO</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C297" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D297" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>zP9Svlzg</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C298" t="n">
+        <v>3</v>
+      </c>
+      <c r="D298" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>McP0d8Q7</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>3.40</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D299"/>
+  <dimension ref="A1:D318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5203,19 +5203,365 @@
           <t>McP0d8Q7</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
+      <c r="B299" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C299" t="n">
+        <v>3</v>
+      </c>
+      <c r="D299" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>OMVUWl2K</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="C300" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D300" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>UuMqRJVb</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="C301" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D301" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>bLD0NyVN</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C302" t="n">
+        <v>3</v>
+      </c>
+      <c r="D302" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>I5fXHFho</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C303" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D303" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>0WfhZq4U</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C304" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D304" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>4vIh2rYG</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>2</v>
+      </c>
+      <c r="C305" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D305" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>zoo3iRJb</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C306" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D306" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>rBlBk5lB</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C307" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D307" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>4QxKmqJN</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C308" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D308" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>zaQy6QYi</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C309" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D309" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>AwpQqzIk</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C310" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D310" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>fB59P6ff</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
         <is>
           <t>3.00</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr">
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>jwaINpP6</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>OjcQLOgJ</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>xY3xTu1n</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
         <is>
           <t>3.40</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>jeAhPc0B</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>GrV1gmkn</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>z9TkrNto</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>8COq4434</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>5.50</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D318"/>
+  <dimension ref="A1:D338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5395,20 +5395,14 @@
           <t>fB59P6ff</t>
         </is>
       </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B311" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C311" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D311" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="312">
@@ -5417,20 +5411,14 @@
           <t>jwaINpP6</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="B312" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C312" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D312" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="313">
@@ -5439,20 +5427,14 @@
           <t>OjcQLOgJ</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
+      <c r="B313" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="C313" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D313" t="n">
+        <v>7.5</v>
       </c>
     </row>
     <row r="314">
@@ -5461,20 +5443,14 @@
           <t>xY3xTu1n</t>
         </is>
       </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="B314" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C314" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D314" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="315">
@@ -5483,20 +5459,14 @@
           <t>jeAhPc0B</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="B315" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C315" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D315" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="316">
@@ -5505,20 +5475,14 @@
           <t>GrV1gmkn</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="B316" t="n">
+        <v>2</v>
+      </c>
+      <c r="C316" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="D316" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="317">
@@ -5527,20 +5491,14 @@
           <t>z9TkrNto</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="B317" t="n">
+        <v>3</v>
+      </c>
+      <c r="C317" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D317" t="n">
+        <v>2.45</v>
       </c>
     </row>
     <row r="318">
@@ -5549,19 +5507,453 @@
           <t>8COq4434</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
+      <c r="B318" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C318" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D318" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>Sp7nVfDF</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
         <is>
           <t>3.60</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr">
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>EssDGebM</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>Y96v2dqT</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
         <is>
           <t>5.50</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>rcXrBZLq</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>IFm4IHT9</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>0b5fTYsS</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>WIDwXGr3</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>Ug79dz7j</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>4CLi9Djd</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>YHET3e9L</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>QFg8dD1e</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>C8Z2IfOE</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>CWHk9jo1</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>WhYYsEn2</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>xjLK5Hv9</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>Um0abZWr</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>WCdGfiW7</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>KYxBGYhR</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>vJJsBCGl</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>3.10</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D338"/>
+  <dimension ref="A1:D358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5523,20 +5523,14 @@
           <t>Sp7nVfDF</t>
         </is>
       </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="B319" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C319" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D319" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="320">
@@ -5545,20 +5539,14 @@
           <t>p2kdKwac</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="B320" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C320" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D320" t="n">
+        <v>2.4</v>
       </c>
     </row>
     <row r="321">
@@ -5567,20 +5555,14 @@
           <t>EssDGebM</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
+      <c r="B321" t="n">
+        <v>5</v>
+      </c>
+      <c r="C321" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D321" t="n">
+        <v>1.7</v>
       </c>
     </row>
     <row r="322">
@@ -5589,20 +5571,14 @@
           <t>Y96v2dqT</t>
         </is>
       </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>9.50</t>
-        </is>
+      <c r="B322" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C322" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D322" t="n">
+        <v>9.5</v>
       </c>
     </row>
     <row r="323">
@@ -5611,20 +5587,14 @@
           <t>rcXrBZLq</t>
         </is>
       </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
+      <c r="B323" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="C323" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D323" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="324">
@@ -5633,20 +5603,14 @@
           <t>IFm4IHT9</t>
         </is>
       </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>8.50</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
+      <c r="B324" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C324" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D324" t="n">
+        <v>1.4</v>
       </c>
     </row>
     <row r="325">
@@ -5655,20 +5619,14 @@
           <t>0b5fTYsS</t>
         </is>
       </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="B325" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C325" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D325" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="326">
@@ -5677,20 +5635,14 @@
           <t>WIDwXGr3</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
+      <c r="B326" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C326" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D326" t="n">
+        <v>2.63</v>
       </c>
     </row>
     <row r="327">
@@ -5699,20 +5651,14 @@
           <t>Ug79dz7j</t>
         </is>
       </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="B327" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C327" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D327" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="328">
@@ -5721,20 +5667,14 @@
           <t>4CLi9Djd</t>
         </is>
       </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="B328" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C328" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D328" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="329">
@@ -5743,20 +5683,14 @@
           <t>YHET3e9L</t>
         </is>
       </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="B329" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C329" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D329" t="n">
+        <v>2.45</v>
       </c>
     </row>
     <row r="330">
@@ -5765,20 +5699,14 @@
           <t>QFg8dD1e</t>
         </is>
       </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
+      <c r="B330" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C330" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D330" t="n">
+        <v>1.9</v>
       </c>
     </row>
     <row r="331">
@@ -5787,20 +5715,14 @@
           <t>C8Z2IfOE</t>
         </is>
       </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="B331" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C331" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D331" t="n">
+        <v>3.7</v>
       </c>
     </row>
     <row r="332">
@@ -5809,20 +5731,14 @@
           <t>CWHk9jo1</t>
         </is>
       </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B332" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C332" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D332" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="333">
@@ -5831,20 +5747,14 @@
           <t>WhYYsEn2</t>
         </is>
       </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="B333" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C333" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D333" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="334">
@@ -5853,20 +5763,14 @@
           <t>xjLK5Hv9</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="B334" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C334" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D334" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="335">
@@ -5875,20 +5779,14 @@
           <t>Um0abZWr</t>
         </is>
       </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="B335" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C335" t="n">
+        <v>3</v>
+      </c>
+      <c r="D335" t="n">
+        <v>2.4</v>
       </c>
     </row>
     <row r="336">
@@ -5897,20 +5795,14 @@
           <t>WCdGfiW7</t>
         </is>
       </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="B336" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C336" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D336" t="n">
+        <v>2.75</v>
       </c>
     </row>
     <row r="337">
@@ -5919,20 +5811,14 @@
           <t>KYxBGYhR</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B337" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C337" t="n">
+        <v>3</v>
+      </c>
+      <c r="D337" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="338">
@@ -5941,19 +5827,351 @@
           <t>vJJsBCGl</t>
         </is>
       </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>3.10</t>
+      <c r="B338" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C338" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D338" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>v5hMsYdL</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="C339" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D339" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>WvkEqfS8</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>5</v>
+      </c>
+      <c r="C340" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D340" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>b7pTwPem</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C341" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D341" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>CCu9YTJ7</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C342" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D342" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>Gpn0zjke</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>6</v>
+      </c>
+      <c r="C343" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D343" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>pOryx3Qa</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C344" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D344" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>rJ8JNC5k</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C345" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D345" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>hKWmMctm</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C346" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D346" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>EZKdKyBa</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C347" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D347" t="n">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>UNG8PBVs</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C348" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D348" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>xlKGNk0f</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>2</v>
+      </c>
+      <c r="C349" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D349" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>WnDPLTU6</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C350" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D350" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>40BXJ7aJ</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C351" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D351" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>MytIRJIP</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C352" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D352" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>Iqmj7UFD</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C353" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D353" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>pjuxVX7K</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C354" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D354" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>0jJ4IFuC</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C355" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="D355" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>rXmhxCKr</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>jqCRLjz2</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>vJXfdXBE</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>4.20</t>
         </is>
       </c>
     </row>
